--- a/Contenidos_Consultados/output/contenidos_consultados_mayo_2026.xlsx
+++ b/Contenidos_Consultados/output/contenidos_consultados_mayo_2026.xlsx
@@ -591,7 +591,7 @@
 7- Hospitales: (75.835)
 8- Licencias: (71.155)
 9- Trámites SAP: (68.275)
-10- Buscar donde está permitido estacionar: (49.844)</t>
+10- Busca donde está permitido estacionar: (49.844)</t>
         </is>
       </c>
     </row>
